--- a/data/trans_orig/P79A2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A2_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15460</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>886</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>24061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26301</t>
+          <t>36053</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>83,41%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,27 +2818,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>385</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>39613</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>57488</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>46715</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65387</t>
+          <t>90492</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>116904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>43634</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
